--- a/site/Okta-UKG-Ready-Integration-Guide/headings.xlsx
+++ b/site/Okta-UKG-Ready-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -727,7 +727,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Delete Conditions</t>
+          <t>Upsert Conditions</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -737,19 +737,19 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KFAQH68KP57FZ86PNGTKPJHE</t>
+          <t>h_01KFAQH9N1WCRQ5BPA36YCWWQC</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Okta-UKG-Ready-Integration-Guide/#h_01KFAQH68KP57FZ86PNGTKPJHE</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Okta-UKG-Ready-Integration-Guide/#h_01KFAQH9N1WCRQ5BPA36YCWWQC</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Upsert Conditions</t>
+          <t>Delete Conditions</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -759,63 +759,63 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01KFAQH9N1WCRQ5BPA36YCWWQC</t>
+          <t>h_01KFAQH68KP57FZ86PNGTKPJHE</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Okta-UKG-Ready-Integration-Guide/#h_01KFAQH9N1WCRQ5BPA36YCWWQC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Okta-UKG-Ready-Integration-Guide/#h_01KFAQH68KP57FZ86PNGTKPJHE</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Logging</t>
+          <t>User Correlation Settings</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01K0PGWJSDQBPT1BZ25EAQGNYR</t>
+          <t>h_01KQ7D1SMBRZPB8WDCJY80RK1B</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Okta-UKG-Ready-Integration-Guide/#h_01K0PGWJSDQBPT1BZ25EAQGNYR</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Okta-UKG-Ready-Integration-Guide/#h_01KQ7D1SMBRZPB8WDCJY80RK1B</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Reporting Settings</t>
+          <t>Safeguard Limits</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>h_01KQ7DBPC2VK71HVHQ99MV0S7Z</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Okta-UKG-Ready-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Okta-UKG-Ready-Integration-Guide/#h_01KQ7DBPC2VK71HVHQ99MV0S7Z</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Insights Settings</t>
+          <t>Logging</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -825,19 +825,19 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01K0PGWJSDXT2R47JVRVF1X192</t>
+          <t>h_01K0PGWJSDQBPT1BZ25EAQGNYR</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Okta-UKG-Ready-Integration-Guide/#h_01K0PGWJSDXT2R47JVRVF1X192</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Okta-UKG-Ready-Integration-Guide/#h_01K0PGWJSDQBPT1BZ25EAQGNYR</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Notification Settings</t>
+          <t>Reporting Settings</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -847,85 +847,85 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01K0EPNYJEHDW4TQRTN6PXT579</t>
+          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Okta-UKG-Ready-Integration-Guide/#h_01K0EPNYJEHDW4TQRTN6PXT579</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Okta-UKG-Ready-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Insights Settings</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01K4SCCHHSQ59XA8AZYDHPC8XW</t>
+          <t>h_01K0PGWJSDXT2R47JVRVF1X192</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Okta-UKG-Ready-Integration-Guide/#h_01K4SCCHHSQ59XA8AZYDHPC8XW</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Okta-UKG-Ready-Integration-Guide/#h_01K0PGWJSDXT2R47JVRVF1X192</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Notification Settings</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01K4SCYQFSS7AMCBA8ENY043BT</t>
+          <t>h_01K0EPNYJEHDW4TQRTN6PXT579</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Okta-UKG-Ready-Integration-Guide/#h_01K4SCYQFSS7AMCBA8ENY043BT</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Okta-UKG-Ready-Integration-Guide/#h_01K0EPNYJEHDW4TQRTN6PXT579</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Create Custom Attributes in Okta</t>
+          <t>Attribute Mapping</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01J6XRXE25YXJE5CJ0RQRJDEF1</t>
+          <t>h_01K4SCCHHSQ59XA8AZYDHPC8XW</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Okta-UKG-Ready-Integration-Guide/#h_01J6XRXE25YXJE5CJ0RQRJDEF1</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Okta-UKG-Ready-Integration-Guide/#h_01K4SCCHHSQ59XA8AZYDHPC8XW</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Map Custom Attribute to Okta Profile</t>
+          <t>Create Custom Attributes in Okta</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -935,19 +935,19 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01J6XV4GBH0QTB86T0TX6YJYWZ</t>
+          <t>h_01J6XRXE25YXJE5CJ0RQRJDEF1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Okta-UKG-Ready-Integration-Guide/#h_01J6XV4GBH0QTB86T0TX6YJYWZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Okta-UKG-Ready-Integration-Guide/#h_01J6XRXE25YXJE5CJ0RQRJDEF1</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Map Custom Attribute to Okta Profile</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -957,32 +957,76 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01J6XV4GBH0QTB86T0TX6YJYWZ</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Okta-UKG-Ready-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Okta-UKG-Ready-Integration-Guide/#h_01J6XV4GBH0QTB86T0TX6YJYWZ</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>h_01K4SCYQFSS7AMCBA8ENY043BT</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Okta-UKG-Ready-Integration-Guide/#h_01K4SCYQFSS7AMCBA8ENY043BT</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Okta-UKG-Ready-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>Additional Options</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Okta-UKG-Ready-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
